--- a/Date & Time Function.xlsx
+++ b/Date & Time Function.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Zaki DA\Excel-Data-Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD136B7C-8364-41DA-A5C0-2A5B20D26A23}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E74D474-C1FC-4FA6-A9DE-C9044FB00FFB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7005" xr2:uid="{0EA24E5C-EB78-4941-BBEC-4F901E993AFC}"/>
   </bookViews>
@@ -589,7 +589,7 @@
       </c>
       <c r="N2">
         <f ca="1">YEARFRAC(M2,TODAY(),3)</f>
-        <v>28.172602739726027</v>
+        <v>28.175342465753424</v>
       </c>
       <c r="O2">
         <f ca="1">ROUND(YEARFRAC(M2,TODAY(),3),0)</f>
@@ -650,7 +650,7 @@
       </c>
       <c r="N3">
         <f t="shared" ref="N3:N20" ca="1" si="8">YEARFRAC(M3,TODAY(),3)</f>
-        <v>24.736986301369864</v>
+        <v>24.739726027397261</v>
       </c>
       <c r="O3">
         <f t="shared" ref="O3:O20" ca="1" si="9">ROUND(YEARFRAC(M3,TODAY(),3),0)</f>
@@ -711,7 +711,7 @@
       </c>
       <c r="N4">
         <f t="shared" ca="1" si="8"/>
-        <v>30.443835616438356</v>
+        <v>30.446575342465753</v>
       </c>
       <c r="O4">
         <f t="shared" ca="1" si="9"/>
@@ -772,7 +772,7 @@
       </c>
       <c r="N5">
         <f t="shared" ca="1" si="8"/>
-        <v>25.884931506849316</v>
+        <v>25.887671232876713</v>
       </c>
       <c r="O5">
         <f t="shared" ca="1" si="9"/>
@@ -833,7 +833,7 @@
       </c>
       <c r="N6">
         <f t="shared" ca="1" si="8"/>
-        <v>29.265753424657536</v>
+        <v>29.268493150684932</v>
       </c>
       <c r="O6">
         <f t="shared" ca="1" si="9"/>
@@ -894,7 +894,7 @@
       </c>
       <c r="N7">
         <f t="shared" ca="1" si="8"/>
-        <v>23.665753424657535</v>
+        <v>23.668493150684931</v>
       </c>
       <c r="O7">
         <f t="shared" ca="1" si="9"/>
@@ -955,7 +955,7 @@
       </c>
       <c r="N8">
         <f t="shared" ca="1" si="8"/>
-        <v>31.317808219178083</v>
+        <v>31.32054794520548</v>
       </c>
       <c r="O8">
         <f t="shared" ca="1" si="9"/>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="N9">
         <f t="shared" ca="1" si="8"/>
-        <v>27.117808219178084</v>
+        <v>27.12054794520548</v>
       </c>
       <c r="O9">
         <f t="shared" ca="1" si="9"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="N10">
         <f t="shared" ca="1" si="8"/>
-        <v>22.824657534246576</v>
+        <v>22.827397260273973</v>
       </c>
       <c r="O10">
         <f t="shared" ca="1" si="9"/>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="N11">
         <f t="shared" ca="1" si="8"/>
-        <v>29.594520547945205</v>
+        <v>29.597260273972601</v>
       </c>
       <c r="O11">
         <f t="shared" ca="1" si="9"/>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="N12">
         <f t="shared" ca="1" si="8"/>
-        <v>28.038356164383561</v>
+        <v>28.041095890410958</v>
       </c>
       <c r="O12">
         <f t="shared" ca="1" si="9"/>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="N13">
         <f t="shared" ca="1" si="8"/>
-        <v>24.473972602739725</v>
+        <v>24.476712328767125</v>
       </c>
       <c r="O13">
         <f t="shared" ca="1" si="9"/>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="N14">
         <f t="shared" ca="1" si="8"/>
-        <v>31.186301369863013</v>
+        <v>31.18904109589041</v>
       </c>
       <c r="O14">
         <f t="shared" ca="1" si="9"/>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="N15">
         <f t="shared" ca="1" si="8"/>
-        <v>25.747945205479454</v>
+        <v>25.75068493150685</v>
       </c>
       <c r="O15">
         <f t="shared" ca="1" si="9"/>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="N16">
         <f t="shared" ca="1" si="8"/>
-        <v>28.375342465753423</v>
+        <v>28.378082191780823</v>
       </c>
       <c r="O16">
         <f t="shared" ca="1" si="9"/>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="N17">
         <f t="shared" ca="1" si="8"/>
-        <v>23.923287671232877</v>
+        <v>23.926027397260274</v>
       </c>
       <c r="O17">
         <f t="shared" ca="1" si="9"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="N18">
         <f t="shared" ca="1" si="8"/>
-        <v>31.641095890410959</v>
+        <v>31.643835616438356</v>
       </c>
       <c r="O18">
         <f t="shared" ca="1" si="9"/>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="N19">
         <f t="shared" ca="1" si="8"/>
-        <v>27.276712328767122</v>
+        <v>27.279452054794522</v>
       </c>
       <c r="O19">
         <f t="shared" ca="1" si="9"/>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="N20">
         <f t="shared" ca="1" si="8"/>
-        <v>22.82191780821918</v>
+        <v>22.824657534246576</v>
       </c>
       <c r="O20">
         <f t="shared" ca="1" si="9"/>
